--- a/data/trans_orig/IP07C12-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45238</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58711</t>
+          <t>58045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74068</t>
+          <t>73220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35982</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>55234</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>72428</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>70,26%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>38701</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>72631</t>
+          <t>72603</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>34292</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>69330</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>135102</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>153625</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>181696</t>
+          <t>180354</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>296265</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>335569</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85757</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>111881</t>
+          <t>112550</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85103</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>111845</t>
+          <t>111615</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,47 +6351,47 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>178597</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>216615</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
           <t>36,21%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>196888</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>179401</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>215682</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24091</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13045</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31493</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48132</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73398</t>
+          <t>73201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86820</t>
+          <t>86875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7815</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>36802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20471</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,47 +9506,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2256</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>34149</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45478</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62986</t>
+          <t>63132</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>27080</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>29175</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25164</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>57932</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>76962</t>
+          <t>77439</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>27991</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>42927</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>30541</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>63066</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>82936</t>
+          <t>83633</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>159205</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>188044</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>168737</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>197669</t>
+          <t>197700</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>335458</t>
+          <t>335088</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>375621</t>
+          <t>375950</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>95968</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,47 +12725,47 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>205119</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>186679</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>225558</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>205119</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>185450</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>224222</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>83439</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>28342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43556</t>
+          <t>43280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63655</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80643</t>
+          <t>80193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20799</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39866</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45937</t>
+          <t>45268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>59537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>805</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20584</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44201</t>
+          <t>44632</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26387</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40065</t>
+          <t>40285</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>27452</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41172</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>56766</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76878</t>
+          <t>76495</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47026</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,47 +17961,47 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>8714</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>1767</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>9048</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38478</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>57592</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>76757</t>
+          <t>77404</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>38298</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>43834</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78250</t>
+          <t>78012</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16545</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>198310</t>
+          <t>197316</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>170115</t>
+          <t>172859</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>204679</t>
+          <t>203809</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>349969</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>392516</t>
+          <t>393692</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>101754</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>137237</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>217401</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>259367</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>83184</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,39 +19403,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
